--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.625</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8125</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J2" t="n">
-        <v>0.78</v>
+        <v>0.6904761904761905</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.780952380952381</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.7966101694915254</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -491,22 +491,22 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.780952380952381</v>
+        <v>0.825</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.7115384615384616</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness_thresholds.xlsx
@@ -491,22 +491,22 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.825</v>
+        <v>0.8310344827586207</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7115384615384616</v>
+        <v>0.7796610169491526</v>
       </c>
     </row>
   </sheetData>
